--- a/data/trans_orig/P24F-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P24F-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le gustaría dejar de fumar en 2007</t>
+          <t>Población según si le gustaría dejar de fumar en 2007 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3910</t>
+          <t>4021</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15212</t>
+          <t>15801</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3701</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13882</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10463</t>
+          <t>10343</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25770</t>
+          <t>25618</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92108</t>
+          <t>90930</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>120201</t>
+          <t>119828</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66208</t>
+          <t>66862</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92248</t>
+          <t>92951</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>168262</t>
+          <t>164634</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>205453</t>
+          <t>203000</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>54,41%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24795</t>
+          <t>24835</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46839</t>
+          <t>46437</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31907</t>
+          <t>31070</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53028</t>
+          <t>52922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>61838</t>
+          <t>61939</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>92351</t>
+          <t>91718</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42905</t>
+          <t>43633</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68176</t>
+          <t>69215</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30396</t>
+          <t>30152</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52786</t>
+          <t>50725</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78112</t>
+          <t>77317</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>111786</t>
+          <t>113105</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,31%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19414</t>
+          <t>21455</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7245</t>
+          <t>8022</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22813</t>
+          <t>21959</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>15915</t>
+          <t>15490</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>36004</t>
+          <t>35944</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>152882</t>
+          <t>154884</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>194367</t>
+          <t>196022</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71061</t>
+          <t>69937</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>99758</t>
+          <t>99317</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>229609</t>
+          <t>235818</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>281368</t>
+          <t>283434</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,78%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113506</t>
+          <t>115650</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>152959</t>
+          <t>153717</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76067</t>
+          <t>75323</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>105973</t>
+          <t>105549</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>202148</t>
+          <t>198273</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>249460</t>
+          <t>247576</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,12%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64547</t>
+          <t>64531</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>99958</t>
+          <t>98922</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35134</t>
+          <t>34438</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>58979</t>
+          <t>59140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>105335</t>
+          <t>107210</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>148518</t>
+          <t>148202</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8424</t>
+          <t>8592</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24376</t>
+          <t>26008</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>8068</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23501</t>
+          <t>23044</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20325</t>
+          <t>19456</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>41328</t>
+          <t>41019</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>106376</t>
+          <t>106015</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>143983</t>
+          <t>143340</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>61398</t>
+          <t>60194</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>91187</t>
+          <t>90027</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>174314</t>
+          <t>176866</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>222903</t>
+          <t>222809</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,23%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>130541</t>
+          <t>128199</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>168109</t>
+          <t>166771</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>115635</t>
+          <t>118199</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>148420</t>
+          <t>149067</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>254810</t>
+          <t>254989</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>303913</t>
+          <t>306399</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>51,2%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38582</t>
+          <t>38718</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>66823</t>
+          <t>67343</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25395</t>
+          <t>25511</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>48171</t>
+          <t>46266</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>70386</t>
+          <t>70611</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>108912</t>
+          <t>108210</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15584</t>
+          <t>15159</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>4998</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17492</t>
+          <t>17282</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>10084</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27011</t>
+          <t>27421</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51090</t>
+          <t>50599</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>79421</t>
+          <t>78889</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36171</t>
+          <t>35668</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58513</t>
+          <t>58773</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>92944</t>
+          <t>92865</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>128623</t>
+          <t>129928</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>34,22%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>104721</t>
+          <t>104936</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>135652</t>
+          <t>137195</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>57529</t>
+          <t>57578</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>81216</t>
+          <t>81341</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>170207</t>
+          <t>171574</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>209755</t>
+          <t>211719</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,76%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30967</t>
+          <t>31789</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56255</t>
+          <t>55681</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11420</t>
+          <t>11609</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27626</t>
+          <t>27590</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47958</t>
+          <t>47471</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>76930</t>
+          <t>75988</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,01%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4865</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17195</t>
+          <t>16851</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5442</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5655</t>
+          <t>5930</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17453</t>
+          <t>17989</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19842</t>
+          <t>18959</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>37437</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10279</t>
+          <t>10116</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23991</t>
+          <t>23215</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33953</t>
+          <t>33825</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>57199</t>
+          <t>56232</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,03%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>56948</t>
+          <t>56358</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>78881</t>
+          <t>78154</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11349</t>
+          <t>11773</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24421</t>
+          <t>24854</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>72589</t>
+          <t>72779</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>97797</t>
+          <t>98449</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>56,07%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>16306</t>
+          <t>15659</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>32577</t>
+          <t>32171</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6903</t>
+          <t>6312</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>19705</t>
+          <t>18174</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>26134</t>
+          <t>25806</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>46755</t>
+          <t>46908</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,72%</t>
         </is>
       </c>
     </row>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6400</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>884</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7194</t>
+          <t>8319</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8823</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>21260</t>
+          <t>21214</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>9174</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>22487</t>
+          <t>22823</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>38,19%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>20924</t>
+          <t>20546</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>34376</t>
+          <t>34834</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>24889</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>39525</t>
+          <t>39359</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>65,86%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5093</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>15687</t>
+          <t>15587</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4478</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>15026</t>
+          <t>15798</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4146,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>791</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>6995</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4196,12 +4196,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>825</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>7650</t>
+          <t>7791</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,55%</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1707</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>9535</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>10463</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>38,34%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3723</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>12799</t>
+          <t>13053</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>15560</t>
+          <t>15373</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>56,34%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3576</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>11853</t>
+          <t>12130</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>15352</t>
+          <t>15028</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>55,07%</t>
         </is>
       </c>
     </row>
@@ -4715,12 +4715,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>41959</t>
+          <t>43728</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>71914</t>
+          <t>72242</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>35269</t>
+          <t>36319</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>61706</t>
+          <t>62014</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4765,12 +4765,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4785,12 +4785,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>84722</t>
+          <t>85139</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>123624</t>
+          <t>123453</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4800,12 +4800,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -4828,12 +4828,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>480607</t>
+          <t>480612</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>550754</t>
+          <t>552610</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>274323</t>
+          <t>276896</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>331182</t>
+          <t>330746</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>775717</t>
+          <t>775211</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>868448</t>
+          <t>864450</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -4941,12 +4941,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>501939</t>
+          <t>505339</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>575240</t>
+          <t>578158</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4956,12 +4956,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>330293</t>
+          <t>329135</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>389451</t>
+          <t>387586</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>852732</t>
+          <t>851167</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>946516</t>
+          <t>944458</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,04%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>239529</t>
+          <t>239947</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>302795</t>
+          <t>301805</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>133553</t>
+          <t>131120</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>177637</t>
+          <t>175777</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>386331</t>
+          <t>390450</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>459901</t>
+          <t>462901</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5324,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le gustaría dejar de fumar en 2012</t>
+          <t>Población según si le gustaría dejar de fumar en 2012 (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11293</t>
+          <t>11247</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7487</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13471</t>
+          <t>14578</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5604,12 +5604,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -5632,12 +5632,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28624</t>
+          <t>27884</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51091</t>
+          <t>49429</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5647,12 +5647,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19540</t>
+          <t>19512</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40757</t>
+          <t>38660</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52685</t>
+          <t>53277</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83098</t>
+          <t>83157</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5717,12 +5717,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,64%</t>
         </is>
       </c>
     </row>
@@ -5745,12 +5745,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>60475</t>
+          <t>61266</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>85054</t>
+          <t>87792</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59050</t>
+          <t>57723</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>83563</t>
+          <t>84026</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>126804</t>
+          <t>128001</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>160612</t>
+          <t>161464</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,73%</t>
         </is>
       </c>
     </row>
@@ -5858,12 +5858,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37156</t>
+          <t>37407</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60642</t>
+          <t>60331</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35548</t>
+          <t>33896</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57595</t>
+          <t>57526</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78494</t>
+          <t>77363</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110722</t>
+          <t>109760</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5943,12 +5943,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,16%</t>
         </is>
       </c>
     </row>
@@ -6088,12 +6088,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12981</t>
+          <t>12894</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6014</t>
+          <t>6534</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14374</t>
+          <t>14299</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -6201,12 +6201,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38887</t>
+          <t>38928</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65372</t>
+          <t>64701</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26926</t>
+          <t>26374</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49501</t>
+          <t>48949</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72567</t>
+          <t>70291</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>106799</t>
+          <t>107039</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -6314,12 +6314,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>184216</t>
+          <t>184448</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>221735</t>
+          <t>221315</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>163985</t>
+          <t>164107</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>192704</t>
+          <t>192228</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>357170</t>
+          <t>357261</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>405885</t>
+          <t>405822</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>67,9%</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6427,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>72996</t>
+          <t>73030</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>105957</t>
+          <t>105264</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23020</t>
+          <t>22905</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44460</t>
+          <t>45653</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>103290</t>
+          <t>101660</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>141167</t>
+          <t>141465</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -6657,12 +6657,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>1819</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>962</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>8936</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>3675</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14777</t>
+          <t>14330</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -6770,12 +6770,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43566</t>
+          <t>42560</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>70252</t>
+          <t>70269</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6785,7 +6785,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24157</t>
+          <t>22977</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>47286</t>
+          <t>46276</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>71857</t>
+          <t>71928</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>107003</t>
+          <t>107362</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,84%</t>
         </is>
       </c>
     </row>
@@ -6883,12 +6883,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>193835</t>
+          <t>194335</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>228857</t>
+          <t>230462</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>131311</t>
+          <t>131711</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>163319</t>
+          <t>163086</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>336288</t>
+          <t>336759</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>384488</t>
+          <t>383761</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,36%</t>
         </is>
       </c>
     </row>
@@ -6996,12 +6996,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39062</t>
+          <t>38994</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>68042</t>
+          <t>67109</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47530</t>
+          <t>47422</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75387</t>
+          <t>75454</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>91881</t>
+          <t>93385</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>130333</t>
+          <t>132668</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2165</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2329</t>
+          <t>2242</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14236</t>
+          <t>13857</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2292</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13778</t>
+          <t>15149</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -7339,12 +7339,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25402</t>
+          <t>25253</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49216</t>
+          <t>50267</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23073</t>
+          <t>22868</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47303</t>
+          <t>44949</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54144</t>
+          <t>53803</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>87126</t>
+          <t>87264</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>177142</t>
+          <t>176843</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>210255</t>
+          <t>210233</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7467,12 +7467,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>145749</t>
+          <t>146124</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>177097</t>
+          <t>177314</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>335903</t>
+          <t>334774</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>380336</t>
+          <t>378078</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>72,67%</t>
         </is>
       </c>
     </row>
@@ -7565,12 +7565,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36709</t>
+          <t>37436</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63966</t>
+          <t>64214</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26423</t>
+          <t>26441</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52154</t>
+          <t>52727</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>70331</t>
+          <t>69428</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>106552</t>
+          <t>105758</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,33%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>986</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8389</t>
+          <t>8079</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4992</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9447</t>
+          <t>10322</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12681</t>
+          <t>12563</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33583</t>
+          <t>33682</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12750</t>
+          <t>12695</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>18446</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>40648</t>
+          <t>40161</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -8021,12 +8021,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>91135</t>
+          <t>90722</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>115975</t>
+          <t>115262</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8036,12 +8036,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34731</t>
+          <t>34513</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>51668</t>
+          <t>51055</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>131871</t>
+          <t>133086</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>161099</t>
+          <t>162246</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>73,05%</t>
         </is>
       </c>
     </row>
@@ -8134,12 +8134,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>17995</t>
+          <t>17275</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>36214</t>
+          <t>37209</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>9458</t>
+          <t>10641</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>25909</t>
+          <t>26423</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8184,12 +8184,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>32098</t>
+          <t>32326</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>57053</t>
+          <t>57569</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8219,12 +8219,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8399,62 +8399,62 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>1971</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>6728</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>10,53%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>1971</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>6561</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14566</t>
+          <t>14606</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>894</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7819</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5018</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>17579</t>
+          <t>18052</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,69%</t>
         </is>
       </c>
     </row>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>24474</t>
+          <t>23011</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>39148</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12325</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8640,12 +8640,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>30472</t>
+          <t>30068</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>47940</t>
+          <t>49111</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>69,9%</t>
         </is>
       </c>
     </row>
@@ -8703,12 +8703,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4940</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>17550</t>
+          <t>17888</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>13358</t>
+          <t>13202</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>11369</t>
+          <t>11524</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>28523</t>
+          <t>27930</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>39,75%</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4261</t>
+          <t>7431</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8968,62 +8968,62 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>1789</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>5454</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>1045</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>6415</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -9046,12 +9046,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>837</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7488</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9061,12 +9061,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>12550</t>
+          <t>12358</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9131,12 +9131,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>42,93%</t>
         </is>
       </c>
     </row>
@@ -9159,12 +9159,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5437</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>15386</t>
+          <t>15262</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9174,12 +9174,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>16421</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9244,12 +9244,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,23%</t>
         </is>
       </c>
     </row>
@@ -9272,12 +9272,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>6339</t>
+          <t>6236</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>15707</t>
+          <t>15927</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9287,12 +9287,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9307,12 +9307,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9322,12 +9322,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9342,12 +9342,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>5472</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>16613</t>
+          <t>16790</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9357,12 +9357,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>58,33%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>13914</t>
+          <t>13569</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>31575</t>
+          <t>33171</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>7647</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>22705</t>
+          <t>22621</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>25232</t>
+          <t>25324</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>47798</t>
+          <t>50165</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -9592,7 +9592,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -9615,12 +9615,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>186772</t>
+          <t>183707</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>242598</t>
+          <t>240272</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9630,12 +9630,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>120730</t>
+          <t>120235</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>168508</t>
+          <t>168334</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9665,12 +9665,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>323074</t>
+          <t>319727</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>394681</t>
+          <t>389484</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9700,12 +9700,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -9728,12 +9728,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>789877</t>
+          <t>792481</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>863752</t>
+          <t>866741</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9743,12 +9743,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9763,12 +9763,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>583909</t>
+          <t>578231</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>646047</t>
+          <t>642317</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9778,12 +9778,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1395667</t>
+          <t>1393728</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1490237</t>
+          <t>1490702</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -9813,12 +9813,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,23%</t>
         </is>
       </c>
     </row>
@@ -9841,12 +9841,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>253111</t>
+          <t>253796</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>314093</t>
+          <t>317323</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -9856,12 +9856,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -9876,12 +9876,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>175560</t>
+          <t>177156</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>227924</t>
+          <t>229306</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -9891,12 +9891,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -9911,12 +9911,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>447121</t>
+          <t>447113</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>524307</t>
+          <t>526317</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -10111,7 +10111,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le gustaría dejar de fumar en 2016</t>
+          <t>Población según si le gustaría dejar de fumar en 2016 (tasa de respuesta: 98,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10306,12 +10306,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13504</t>
+          <t>13776</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10341,12 +10341,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12185</t>
+          <t>11675</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10376,12 +10376,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>7004</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21066</t>
+          <t>20905</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -10419,12 +10419,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27331</t>
+          <t>28410</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50255</t>
+          <t>50346</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10434,12 +10434,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10454,12 +10454,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25105</t>
+          <t>24661</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44485</t>
+          <t>44591</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10489,12 +10489,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58183</t>
+          <t>57654</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86917</t>
+          <t>86853</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,61%</t>
         </is>
       </c>
     </row>
@@ -10532,12 +10532,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43321</t>
+          <t>44668</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66632</t>
+          <t>67685</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10547,12 +10547,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10567,12 +10567,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36950</t>
+          <t>38402</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>57706</t>
+          <t>58592</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10602,12 +10602,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>86952</t>
+          <t>86531</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>119293</t>
+          <t>117868</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,33%</t>
         </is>
       </c>
     </row>
@@ -10645,12 +10645,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28593</t>
+          <t>28468</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49764</t>
+          <t>48812</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10660,12 +10660,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11291</t>
+          <t>11455</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26698</t>
+          <t>26797</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10695,12 +10695,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10715,12 +10715,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43532</t>
+          <t>44007</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72045</t>
+          <t>70684</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10730,12 +10730,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>28,98%</t>
         </is>
       </c>
     </row>
@@ -10875,12 +10875,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10557</t>
+          <t>11113</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10890,12 +10890,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10910,12 +10910,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>2954</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12753</t>
+          <t>12710</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10925,12 +10925,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10945,12 +10945,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6423</t>
+          <t>5857</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19761</t>
+          <t>19344</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10960,12 +10960,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -10988,12 +10988,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47951</t>
+          <t>49234</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76773</t>
+          <t>77007</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11003,12 +11003,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11023,12 +11023,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36476</t>
+          <t>36128</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60397</t>
+          <t>59760</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11038,12 +11038,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11058,12 +11058,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>93653</t>
+          <t>92830</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>129015</t>
+          <t>130591</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11073,12 +11073,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,78%</t>
         </is>
       </c>
     </row>
@@ -11101,12 +11101,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>121791</t>
+          <t>122052</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>154357</t>
+          <t>154389</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11116,12 +11116,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11136,12 +11136,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>100260</t>
+          <t>100702</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>129350</t>
+          <t>128762</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11151,12 +11151,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11171,12 +11171,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>230253</t>
+          <t>229841</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>272970</t>
+          <t>273680</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11186,12 +11186,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,22%</t>
         </is>
       </c>
     </row>
@@ -11214,12 +11214,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41414</t>
+          <t>41702</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67351</t>
+          <t>71763</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11229,12 +11229,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11249,12 +11249,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32318</t>
+          <t>32776</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55320</t>
+          <t>54870</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11264,12 +11264,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11284,12 +11284,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>80286</t>
+          <t>79823</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>114016</t>
+          <t>113801</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11299,12 +11299,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,21%</t>
         </is>
       </c>
     </row>
@@ -11444,12 +11444,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4191</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16339</t>
+          <t>15582</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11459,82 +11459,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>4539</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1713</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>10095</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>13587</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>7706</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>22364</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>1,59%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6,19%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>4539</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1776</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>9977</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>4,54%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>13587</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>7431</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>21723</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -11557,12 +11557,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30096</t>
+          <t>30034</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53998</t>
+          <t>55530</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11572,12 +11572,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11592,12 +11592,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26008</t>
+          <t>25664</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>48140</t>
+          <t>46811</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11607,12 +11607,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11627,12 +11627,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>61406</t>
+          <t>61190</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>93946</t>
+          <t>93348</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11642,12 +11642,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,3%</t>
         </is>
       </c>
     </row>
@@ -11670,12 +11670,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>130668</t>
+          <t>130344</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>162977</t>
+          <t>163325</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11685,12 +11685,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11705,12 +11705,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>114746</t>
+          <t>113890</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>143940</t>
+          <t>142322</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11720,12 +11720,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11740,12 +11740,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>254185</t>
+          <t>253291</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>299091</t>
+          <t>299679</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11755,12 +11755,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>61,97%</t>
         </is>
       </c>
     </row>
@@ -11783,12 +11783,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53741</t>
+          <t>54574</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>81006</t>
+          <t>81556</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11818,12 +11818,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38583</t>
+          <t>39455</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63854</t>
+          <t>62572</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11833,12 +11833,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11853,12 +11853,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>98324</t>
+          <t>96751</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>137044</t>
+          <t>136671</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,26%</t>
         </is>
       </c>
     </row>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15579</t>
+          <t>16622</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12053,7 +12053,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>6496</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4816</t>
+          <t>4795</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18020</t>
+          <t>18634</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12098,12 +12098,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -12126,12 +12126,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40312</t>
+          <t>40233</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>68454</t>
+          <t>69817</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28616</t>
+          <t>27771</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>54077</t>
+          <t>51664</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>75141</t>
+          <t>74255</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>113899</t>
+          <t>112088</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12211,12 +12211,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -12239,12 +12239,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>144507</t>
+          <t>143310</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>177588</t>
+          <t>178870</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12274,12 +12274,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>134493</t>
+          <t>134235</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>165532</t>
+          <t>165121</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12289,12 +12289,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12309,12 +12309,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>286282</t>
+          <t>289513</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>333663</t>
+          <t>331722</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12324,12 +12324,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,03%</t>
         </is>
       </c>
     </row>
@@ -12352,12 +12352,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37076</t>
+          <t>37855</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65505</t>
+          <t>65395</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12387,12 +12387,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27428</t>
+          <t>27159</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51138</t>
+          <t>51743</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12402,12 +12402,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12422,12 +12422,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>72108</t>
+          <t>71899</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>108263</t>
+          <t>106981</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12437,12 +12437,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -12587,7 +12587,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5902</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12602,7 +12602,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>9786</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12637,7 +12637,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11845</t>
+          <t>11844</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12667,7 +12667,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16087</t>
+          <t>15662</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>34129</t>
+          <t>34508</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15101</t>
+          <t>15890</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34530</t>
+          <t>33476</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>36050</t>
+          <t>35170</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>63332</t>
+          <t>61746</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -12808,12 +12808,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>87131</t>
+          <t>87093</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>108880</t>
+          <t>109993</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>45654</t>
+          <t>45459</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>67997</t>
+          <t>68040</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>137469</t>
+          <t>137173</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>172161</t>
+          <t>171717</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12893,12 +12893,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>66,67%</t>
         </is>
       </c>
     </row>
@@ -12921,12 +12921,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14424</t>
+          <t>13745</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>33269</t>
+          <t>32007</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12956,12 +12956,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>17758</t>
+          <t>17622</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>37364</t>
+          <t>37797</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>37045</t>
+          <t>37302</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>64921</t>
+          <t>63906</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13006,12 +13006,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>24,81%</t>
         </is>
       </c>
     </row>
@@ -13151,12 +13151,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>915</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>7421</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13166,12 +13166,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13201,12 +13201,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>884</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7487</t>
+          <t>8266</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13236,12 +13236,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -13264,12 +13264,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2169</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13607</t>
+          <t>14264</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13279,12 +13279,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9754</t>
+          <t>9538</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13314,12 +13314,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5984</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18599</t>
+          <t>19002</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13349,12 +13349,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -13377,12 +13377,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>29115</t>
+          <t>29215</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>44103</t>
+          <t>43974</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13392,12 +13392,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>11377</t>
+          <t>11511</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>23104</t>
+          <t>22870</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13427,12 +13427,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>45241</t>
+          <t>44084</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>63923</t>
+          <t>63747</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13462,12 +13462,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,23%</t>
         </is>
       </c>
     </row>
@@ -13490,12 +13490,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>18514</t>
+          <t>17926</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13505,12 +13505,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3811</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>14419</t>
+          <t>14741</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13540,12 +13540,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>12092</t>
+          <t>11492</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>28506</t>
+          <t>28505</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -13575,7 +13575,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -13720,97 +13720,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>1513</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>2117</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>26,42%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>1693</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -13833,12 +13833,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>739</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6444</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -13883,12 +13883,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>721</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>6056</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -13923,7 +13923,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -13946,12 +13946,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>8231</t>
+          <t>8348</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>16599</t>
+          <t>16536</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13981,7 +13981,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>2779</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -13996,7 +13996,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>13886</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>23915</t>
+          <t>24199</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14031,12 +14031,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,96%</t>
         </is>
       </c>
     </row>
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>12498</t>
+          <t>12377</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14074,12 +14074,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14114,7 +14114,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>14152</t>
+          <t>14410</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14144,12 +14144,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>46,42%</t>
         </is>
       </c>
     </row>
@@ -14289,12 +14289,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>22930</t>
+          <t>22748</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>46452</t>
+          <t>46625</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -14304,12 +14304,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -14324,12 +14324,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>14974</t>
+          <t>14646</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>33489</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -14339,12 +14339,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -14359,12 +14359,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>42513</t>
+          <t>42262</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>72600</t>
+          <t>71243</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -14374,12 +14374,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -14402,12 +14402,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>199312</t>
+          <t>204103</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>259409</t>
+          <t>260841</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14417,12 +14417,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>158616</t>
+          <t>159086</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>208637</t>
+          <t>208274</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14452,12 +14452,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>374471</t>
+          <t>374979</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>452268</t>
+          <t>449093</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14487,12 +14487,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -14515,12 +14515,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>614349</t>
+          <t>612150</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>682997</t>
+          <t>681503</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14530,12 +14530,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>491422</t>
+          <t>491200</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>551755</t>
+          <t>551729</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -14565,12 +14565,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1128989</t>
+          <t>1122715</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1218215</t>
+          <t>1214632</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -14600,12 +14600,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,49%</t>
         </is>
       </c>
     </row>
@@ -14628,12 +14628,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>222344</t>
+          <t>219290</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>277521</t>
+          <t>280960</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -14643,12 +14643,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>159466</t>
+          <t>162480</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>212258</t>
+          <t>210310</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -14678,12 +14678,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>397162</t>
+          <t>400894</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>473711</t>
+          <t>476394</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -14713,12 +14713,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P24F-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P24F-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15801</t>
+          <t>15328</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>2994</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14169</t>
+          <t>14537</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10343</t>
+          <t>10115</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25618</t>
+          <t>25486</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90930</t>
+          <t>92144</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>119828</t>
+          <t>120788</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66862</t>
+          <t>67378</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92951</t>
+          <t>91617</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>164634</t>
+          <t>168050</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>203000</t>
+          <t>205542</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>55,09%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24835</t>
+          <t>24828</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46437</t>
+          <t>47638</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31070</t>
+          <t>31485</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52922</t>
+          <t>53517</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>61939</t>
+          <t>61017</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91718</t>
+          <t>90309</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,21%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43633</t>
+          <t>42501</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69215</t>
+          <t>67972</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30152</t>
+          <t>29977</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50725</t>
+          <t>52267</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>77317</t>
+          <t>78351</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113105</t>
+          <t>111825</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>29,97%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>5453</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21455</t>
+          <t>20687</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>7239</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21959</t>
+          <t>22650</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>15490</t>
+          <t>15227</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>35944</t>
+          <t>35199</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>154884</t>
+          <t>154264</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>196022</t>
+          <t>194672</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>69937</t>
+          <t>68462</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>99317</t>
+          <t>99424</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>235818</t>
+          <t>233914</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>283434</t>
+          <t>284721</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,99%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>115650</t>
+          <t>115374</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>153717</t>
+          <t>154449</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75323</t>
+          <t>75437</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>105549</t>
+          <t>104143</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>198273</t>
+          <t>200603</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>247576</t>
+          <t>247264</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,07%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64531</t>
+          <t>65385</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>98922</t>
+          <t>97835</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34438</t>
+          <t>33672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59140</t>
+          <t>59918</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>107210</t>
+          <t>106034</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>148202</t>
+          <t>147748</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8592</t>
+          <t>8679</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26008</t>
+          <t>25282</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8068</t>
+          <t>8225</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23044</t>
+          <t>22700</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19456</t>
+          <t>20545</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>41019</t>
+          <t>43385</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>106015</t>
+          <t>106361</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>143340</t>
+          <t>141743</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>60194</t>
+          <t>60916</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>90027</t>
+          <t>90155</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>176866</t>
+          <t>176580</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>222809</t>
+          <t>221012</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>36,93%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>128199</t>
+          <t>131084</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>166771</t>
+          <t>166908</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>118199</t>
+          <t>115434</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>149067</t>
+          <t>149333</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>254989</t>
+          <t>256853</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>306399</t>
+          <t>305483</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,05%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38718</t>
+          <t>39704</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67343</t>
+          <t>66129</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25511</t>
+          <t>25344</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46266</t>
+          <t>47176</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>70611</t>
+          <t>72839</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>108210</t>
+          <t>107423</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15159</t>
+          <t>14563</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4998</t>
+          <t>4894</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17282</t>
+          <t>16993</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10084</t>
+          <t>10584</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27421</t>
+          <t>27784</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50599</t>
+          <t>51528</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>78889</t>
+          <t>79481</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35668</t>
+          <t>35428</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58773</t>
+          <t>58410</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>92865</t>
+          <t>93239</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>129928</t>
+          <t>131413</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>104936</t>
+          <t>104219</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>137195</t>
+          <t>135981</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>57578</t>
+          <t>58169</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>81341</t>
+          <t>81487</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>171574</t>
+          <t>169771</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>211719</t>
+          <t>212905</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>56,07%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31789</t>
+          <t>31808</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55681</t>
+          <t>55367</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11609</t>
+          <t>12314</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27590</t>
+          <t>27708</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47471</t>
+          <t>47709</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>75988</t>
+          <t>76096</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,04%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16851</t>
+          <t>16671</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5930</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17989</t>
+          <t>18466</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18959</t>
+          <t>18968</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37437</t>
+          <t>37295</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10116</t>
+          <t>9980</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23215</t>
+          <t>23339</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33825</t>
+          <t>32863</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>56232</t>
+          <t>55760</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,76%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>56358</t>
+          <t>56835</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>78154</t>
+          <t>79103</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11773</t>
+          <t>11751</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24854</t>
+          <t>25217</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>72779</t>
+          <t>72348</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>98449</t>
+          <t>98556</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,13%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>15659</t>
+          <t>15089</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>32171</t>
+          <t>32448</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6312</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>18174</t>
+          <t>18100</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>25806</t>
+          <t>26165</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>46908</t>
+          <t>46615</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,55%</t>
         </is>
       </c>
     </row>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>2811</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>872</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8319</t>
+          <t>7413</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9062</t>
+          <t>8654</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>21214</t>
+          <t>20837</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>9672</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>22823</t>
+          <t>22417</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,51%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>20546</t>
+          <t>21148</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>34834</t>
+          <t>34607</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24780</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>39359</t>
+          <t>39311</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,78%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5093</t>
+          <t>4968</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>15587</t>
+          <t>16444</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>15798</t>
+          <t>16561</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>27,71%</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4146,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>786</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6995</t>
+          <t>7172</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>822</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>7164</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>26,25%</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9535</t>
+          <t>9884</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>10463</t>
+          <t>10585</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,79%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13053</t>
+          <t>12891</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>15373</t>
+          <t>15171</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>55,59%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>12130</t>
+          <t>11819</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>4839</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>15028</t>
+          <t>14794</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>54,22%</t>
         </is>
       </c>
     </row>
@@ -4715,12 +4715,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>43728</t>
+          <t>42325</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>72242</t>
+          <t>72463</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>36319</t>
+          <t>34837</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>62014</t>
+          <t>61009</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4765,12 +4765,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4785,12 +4785,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>85139</t>
+          <t>85318</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>123453</t>
+          <t>125985</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4800,12 +4800,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -4828,12 +4828,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>480612</t>
+          <t>481172</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>552610</t>
+          <t>555753</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>276896</t>
+          <t>272821</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>330746</t>
+          <t>329354</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>775211</t>
+          <t>775466</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>864450</t>
+          <t>866010</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,54%</t>
         </is>
       </c>
     </row>
@@ -4941,12 +4941,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>505339</t>
+          <t>503800</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>578158</t>
+          <t>577745</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4956,12 +4956,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>329135</t>
+          <t>329903</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>387586</t>
+          <t>387843</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>851167</t>
+          <t>854570</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>944458</t>
+          <t>950365</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,3%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>239947</t>
+          <t>240708</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>301805</t>
+          <t>300911</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>131120</t>
+          <t>132167</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>175777</t>
+          <t>177644</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>390450</t>
+          <t>387870</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>462901</t>
+          <t>463161</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11247</t>
+          <t>11467</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>8668</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14578</t>
+          <t>14019</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5604,12 +5604,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -5632,12 +5632,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27884</t>
+          <t>28591</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49429</t>
+          <t>48943</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5647,12 +5647,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19512</t>
+          <t>18855</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38660</t>
+          <t>38778</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53277</t>
+          <t>52712</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83157</t>
+          <t>82653</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5717,12 +5717,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,48%</t>
         </is>
       </c>
     </row>
@@ -5745,12 +5745,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>61266</t>
+          <t>59352</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87792</t>
+          <t>85741</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>57723</t>
+          <t>59794</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>84026</t>
+          <t>82670</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>128001</t>
+          <t>127570</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>161464</t>
+          <t>161785</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,83%</t>
         </is>
       </c>
     </row>
@@ -5858,12 +5858,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37407</t>
+          <t>37985</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60331</t>
+          <t>60155</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33896</t>
+          <t>35375</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57526</t>
+          <t>56280</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>77363</t>
+          <t>78562</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109760</t>
+          <t>110653</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5943,12 +5943,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,45%</t>
         </is>
       </c>
     </row>
@@ -6088,12 +6088,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12894</t>
+          <t>12291</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6534</t>
+          <t>5643</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14299</t>
+          <t>13523</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -6201,12 +6201,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38928</t>
+          <t>39459</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64701</t>
+          <t>65793</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26374</t>
+          <t>26510</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48949</t>
+          <t>48948</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70291</t>
+          <t>71328</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>107039</t>
+          <t>105601</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -6314,12 +6314,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>184448</t>
+          <t>185214</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>221315</t>
+          <t>222252</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>164107</t>
+          <t>164032</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>192228</t>
+          <t>191732</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>357261</t>
+          <t>359177</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>405822</t>
+          <t>406647</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>68,04%</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6427,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>73030</t>
+          <t>72386</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>105264</t>
+          <t>106456</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22905</t>
+          <t>23824</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45653</t>
+          <t>46383</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>101660</t>
+          <t>101575</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>141465</t>
+          <t>139878</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,4%</t>
         </is>
       </c>
     </row>
@@ -6657,12 +6657,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>1836</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9897</t>
+          <t>10312</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>956</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>8243</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3675</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14330</t>
+          <t>15383</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -6770,12 +6770,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>42560</t>
+          <t>43044</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>70269</t>
+          <t>69639</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22977</t>
+          <t>24603</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>46276</t>
+          <t>47225</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>71928</t>
+          <t>72523</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>107362</t>
+          <t>108255</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,0%</t>
         </is>
       </c>
     </row>
@@ -6883,12 +6883,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>194335</t>
+          <t>195264</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>230462</t>
+          <t>230259</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>131711</t>
+          <t>132380</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>163086</t>
+          <t>163798</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>336759</t>
+          <t>337021</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>383761</t>
+          <t>383557</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,32%</t>
         </is>
       </c>
     </row>
@@ -6996,12 +6996,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38994</t>
+          <t>39495</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67109</t>
+          <t>67279</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47422</t>
+          <t>46921</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75454</t>
+          <t>74334</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>93385</t>
+          <t>93221</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>132668</t>
+          <t>130194</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2242</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13857</t>
+          <t>13221</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15149</t>
+          <t>14471</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -7339,12 +7339,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25253</t>
+          <t>25680</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50267</t>
+          <t>48541</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22868</t>
+          <t>22376</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44949</t>
+          <t>46219</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>53803</t>
+          <t>53761</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>87264</t>
+          <t>85538</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>176843</t>
+          <t>178115</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>210233</t>
+          <t>210427</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7467,12 +7467,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>146124</t>
+          <t>147401</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>177314</t>
+          <t>179019</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>334774</t>
+          <t>333580</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>378078</t>
+          <t>378456</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,75%</t>
         </is>
       </c>
     </row>
@@ -7565,12 +7565,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37436</t>
+          <t>37572</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64214</t>
+          <t>64336</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26441</t>
+          <t>27090</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52727</t>
+          <t>52646</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>69428</t>
+          <t>70171</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>105758</t>
+          <t>107301</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,63%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8079</t>
+          <t>8441</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>5451</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>9354</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12563</t>
+          <t>12687</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33682</t>
+          <t>32451</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12695</t>
+          <t>12841</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18446</t>
+          <t>17980</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>40161</t>
+          <t>40357</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -8021,12 +8021,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>90722</t>
+          <t>90514</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>115262</t>
+          <t>115342</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8036,12 +8036,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34513</t>
+          <t>34558</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>51055</t>
+          <t>51778</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>133086</t>
+          <t>129678</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>162246</t>
+          <t>161411</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,67%</t>
         </is>
       </c>
     </row>
@@ -8134,12 +8134,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>17275</t>
+          <t>17678</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>37209</t>
+          <t>37479</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>10641</t>
+          <t>9890</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>26423</t>
+          <t>26183</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8184,12 +8184,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>32326</t>
+          <t>30656</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>57569</t>
+          <t>55816</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8219,12 +8219,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7053</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>6387</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14606</t>
+          <t>14696</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>926</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>7664</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>4653</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18052</t>
+          <t>17972</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,58%</t>
         </is>
       </c>
     </row>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>23011</t>
+          <t>23511</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>39580</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12571</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8640,12 +8640,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>30068</t>
+          <t>30117</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>49111</t>
+          <t>48749</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,39%</t>
         </is>
       </c>
     </row>
@@ -8703,12 +8703,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>17888</t>
+          <t>17648</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>13202</t>
+          <t>12708</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>11524</t>
+          <t>11692</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>27930</t>
+          <t>28622</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>40,74%</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5454</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -9046,12 +9046,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>838</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>7477</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9061,12 +9061,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>12358</t>
+          <t>11935</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9131,12 +9131,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>41,46%</t>
         </is>
       </c>
     </row>
@@ -9159,12 +9159,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4556</t>
+          <t>5433</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>15262</t>
+          <t>15192</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9174,12 +9174,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>6356</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>16474</t>
+          <t>16898</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9244,12 +9244,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>58,7%</t>
         </is>
       </c>
     </row>
@@ -9272,12 +9272,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>6402</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>15927</t>
+          <t>16145</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9287,12 +9287,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9342,12 +9342,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>5539</t>
+          <t>5368</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>16790</t>
+          <t>16738</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9357,12 +9357,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>58,14%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>13569</t>
+          <t>13874</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>33171</t>
+          <t>33475</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>7324</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>22621</t>
+          <t>22927</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>25324</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>50165</t>
+          <t>48169</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -9615,12 +9615,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>183707</t>
+          <t>185735</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>240272</t>
+          <t>240356</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9630,12 +9630,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>120235</t>
+          <t>121677</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>168334</t>
+          <t>167330</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9665,12 +9665,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>319727</t>
+          <t>319466</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>389484</t>
+          <t>392662</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9700,12 +9700,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -9728,12 +9728,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>792481</t>
+          <t>792612</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>866741</t>
+          <t>867469</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9763,12 +9763,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>578231</t>
+          <t>581987</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>642317</t>
+          <t>644571</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9778,12 +9778,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1393728</t>
+          <t>1390516</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1490702</t>
+          <t>1486904</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -9813,12 +9813,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,06%</t>
         </is>
       </c>
     </row>
@@ -9841,12 +9841,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>253796</t>
+          <t>254205</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>317323</t>
+          <t>314631</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -9856,12 +9856,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -9876,12 +9876,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>177156</t>
+          <t>176116</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>229306</t>
+          <t>230053</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -9891,12 +9891,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -9911,12 +9911,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>447113</t>
+          <t>448551</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>526317</t>
+          <t>533812</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -9926,12 +9926,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -10306,12 +10306,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3121</t>
+          <t>3063</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13776</t>
+          <t>13746</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10341,12 +10341,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11675</t>
+          <t>11174</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10376,12 +10376,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>6869</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20905</t>
+          <t>21748</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -10419,12 +10419,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28410</t>
+          <t>28188</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50346</t>
+          <t>50916</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10434,12 +10434,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10454,12 +10454,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24661</t>
+          <t>26087</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44591</t>
+          <t>43753</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10489,12 +10489,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57654</t>
+          <t>59212</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86853</t>
+          <t>87841</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>36,02%</t>
         </is>
       </c>
     </row>
@@ -10532,12 +10532,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44668</t>
+          <t>44316</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67685</t>
+          <t>67414</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10547,82 +10547,82 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t>48,35%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>47301</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>37712</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>56983</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>45,29%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>36,11%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>54,56%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>102771</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>88363</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>118375</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>42,14%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>36,23%</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
           <t>48,54%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>47301</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>38402</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>58592</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>45,29%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>36,77%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>56,1%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>102771</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>86531</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>117868</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>42,14%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>35,48%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>48,33%</t>
         </is>
       </c>
     </row>
@@ -10645,12 +10645,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28468</t>
+          <t>28578</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48812</t>
+          <t>49759</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10660,12 +10660,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>11541</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26797</t>
+          <t>27562</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10695,12 +10695,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10715,12 +10715,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44007</t>
+          <t>44530</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70684</t>
+          <t>70309</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10730,12 +10730,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -10875,12 +10875,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1889</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>10613</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10890,12 +10890,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10910,12 +10910,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12710</t>
+          <t>13475</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10925,12 +10925,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10945,12 +10945,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5857</t>
+          <t>5958</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19344</t>
+          <t>19435</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10960,12 +10960,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -10988,12 +10988,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49234</t>
+          <t>49101</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77007</t>
+          <t>77999</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11003,12 +11003,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11023,12 +11023,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36128</t>
+          <t>36764</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59760</t>
+          <t>60384</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11038,12 +11038,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11058,12 +11058,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92830</t>
+          <t>91398</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130591</t>
+          <t>130449</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11073,12 +11073,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,75%</t>
         </is>
       </c>
     </row>
@@ -11101,12 +11101,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>122052</t>
+          <t>121503</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>154389</t>
+          <t>153204</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11116,12 +11116,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11136,12 +11136,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>100702</t>
+          <t>100220</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128762</t>
+          <t>128381</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11151,12 +11151,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11171,12 +11171,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>229841</t>
+          <t>228952</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>273680</t>
+          <t>273782</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11186,12 +11186,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,25%</t>
         </is>
       </c>
     </row>
@@ -11214,12 +11214,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41702</t>
+          <t>42696</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>71763</t>
+          <t>68280</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11229,12 +11229,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11249,12 +11249,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32776</t>
+          <t>31630</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>54870</t>
+          <t>54742</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11264,12 +11264,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11284,12 +11284,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>79823</t>
+          <t>79829</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>113801</t>
+          <t>115411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -11444,12 +11444,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>4152</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15582</t>
+          <t>16217</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11459,82 +11459,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>4539</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1765</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>9598</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>4,37%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>13587</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>7659</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>22105</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>1,58%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>4539</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>10095</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>13587</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>7706</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>22364</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -11557,12 +11557,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30034</t>
+          <t>30927</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55530</t>
+          <t>55054</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11572,12 +11572,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11592,12 +11592,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25664</t>
+          <t>25854</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>46811</t>
+          <t>46138</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11607,12 +11607,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11627,12 +11627,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>61190</t>
+          <t>62440</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>93348</t>
+          <t>94499</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11642,12 +11642,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -11670,12 +11670,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>130344</t>
+          <t>130235</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>163325</t>
+          <t>162843</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11685,12 +11685,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11705,12 +11705,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>113890</t>
+          <t>114919</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142322</t>
+          <t>144323</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11720,12 +11720,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11740,12 +11740,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>253291</t>
+          <t>252032</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>299679</t>
+          <t>296662</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11755,12 +11755,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,35%</t>
         </is>
       </c>
     </row>
@@ -11783,12 +11783,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54574</t>
+          <t>53432</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>81556</t>
+          <t>81244</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11818,12 +11818,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39455</t>
+          <t>38044</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62572</t>
+          <t>64038</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11833,12 +11833,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11853,12 +11853,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>96751</t>
+          <t>98497</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>136671</t>
+          <t>136703</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,27%</t>
         </is>
       </c>
     </row>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16622</t>
+          <t>15645</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12053,7 +12053,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6496</t>
+          <t>7150</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18634</t>
+          <t>17845</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12098,12 +12098,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -12126,12 +12126,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40233</t>
+          <t>40209</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>69817</t>
+          <t>69462</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27771</t>
+          <t>28613</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51664</t>
+          <t>53234</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>74255</t>
+          <t>75112</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>112088</t>
+          <t>111069</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12211,12 +12211,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -12239,12 +12239,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>143310</t>
+          <t>144044</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>178870</t>
+          <t>178619</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12274,12 +12274,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>134235</t>
+          <t>133932</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>165121</t>
+          <t>164450</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12289,12 +12289,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12309,12 +12309,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>289513</t>
+          <t>286865</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>331722</t>
+          <t>334608</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12324,12 +12324,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,61%</t>
         </is>
       </c>
     </row>
@@ -12352,12 +12352,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37855</t>
+          <t>38534</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65395</t>
+          <t>65554</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12387,12 +12387,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27159</t>
+          <t>27862</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51743</t>
+          <t>52022</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12402,12 +12402,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12422,12 +12422,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>71899</t>
+          <t>71350</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>106981</t>
+          <t>109253</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12437,12 +12437,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -12587,7 +12587,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>5412</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12602,7 +12602,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9786</t>
+          <t>10531</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2108</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11844</t>
+          <t>11880</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12667,12 +12667,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -12695,12 +12695,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15662</t>
+          <t>15850</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>34508</t>
+          <t>34162</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15890</t>
+          <t>15324</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33476</t>
+          <t>33736</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>35170</t>
+          <t>35886</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>61746</t>
+          <t>62042</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,09%</t>
         </is>
       </c>
     </row>
@@ -12808,12 +12808,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>87093</t>
+          <t>86090</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>109993</t>
+          <t>109083</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>45459</t>
+          <t>46068</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>68040</t>
+          <t>68118</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>137173</t>
+          <t>137958</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>171717</t>
+          <t>169938</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12893,12 +12893,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>65,98%</t>
         </is>
       </c>
     </row>
@@ -12921,12 +12921,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>13745</t>
+          <t>15223</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>32007</t>
+          <t>32901</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12956,12 +12956,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>17622</t>
+          <t>18346</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>37797</t>
+          <t>39001</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>37302</t>
+          <t>37852</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>63906</t>
+          <t>64734</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13006,12 +13006,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -13151,12 +13151,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>892</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7421</t>
+          <t>8259</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13166,12 +13166,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>893</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8266</t>
+          <t>8315</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13236,12 +13236,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -13264,12 +13264,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14264</t>
+          <t>13518</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13279,12 +13279,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9538</t>
+          <t>8957</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13314,12 +13314,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5984</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>19002</t>
+          <t>18727</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13349,12 +13349,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,22%</t>
         </is>
       </c>
     </row>
@@ -13377,12 +13377,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>29215</t>
+          <t>29434</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>43974</t>
+          <t>44298</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13392,12 +13392,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>11511</t>
+          <t>11507</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>22870</t>
+          <t>22850</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13427,12 +13427,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>44084</t>
+          <t>45244</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>63747</t>
+          <t>63229</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13462,12 +13462,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>71,64%</t>
         </is>
       </c>
     </row>
@@ -13490,12 +13490,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>17926</t>
+          <t>18065</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13505,12 +13505,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3769</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>14741</t>
+          <t>14625</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13540,12 +13540,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>11492</t>
+          <t>12545</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>28505</t>
+          <t>27821</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -13575,12 +13575,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>31,52%</t>
         </is>
       </c>
     </row>
@@ -13833,12 +13833,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>736</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6444</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>717</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>5928</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -13918,12 +13918,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -13946,12 +13946,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>8348</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>16536</t>
+          <t>16620</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13981,7 +13981,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2779</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -13996,7 +13996,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>14170</t>
+          <t>13961</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>24199</t>
+          <t>23813</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14031,12 +14031,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>76,71%</t>
         </is>
       </c>
     </row>
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>12377</t>
+          <t>12429</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14074,12 +14074,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14114,7 +14114,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>5207</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>14410</t>
+          <t>14774</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14144,12 +14144,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>47,59%</t>
         </is>
       </c>
     </row>
@@ -14289,12 +14289,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>22748</t>
+          <t>23438</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>46625</t>
+          <t>46624</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -14304,7 +14304,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -14324,12 +14324,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>14646</t>
+          <t>15834</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>33681</t>
+          <t>34599</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -14339,12 +14339,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -14359,12 +14359,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>42262</t>
+          <t>43597</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>71243</t>
+          <t>73105</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -14374,12 +14374,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -14402,12 +14402,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>204103</t>
+          <t>201590</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>260841</t>
+          <t>259692</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14417,12 +14417,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>159086</t>
+          <t>160201</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>208035</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14452,12 +14452,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>374979</t>
+          <t>372805</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>449093</t>
+          <t>448824</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14487,12 +14487,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,61%</t>
         </is>
       </c>
     </row>
@@ -14515,12 +14515,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>612150</t>
+          <t>611752</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>681503</t>
+          <t>683084</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14530,12 +14530,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>491200</t>
+          <t>490928</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>551729</t>
+          <t>552543</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -14565,12 +14565,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1122715</t>
+          <t>1126482</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1214632</t>
+          <t>1219628</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -14600,12 +14600,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,73%</t>
         </is>
       </c>
     </row>
@@ -14628,12 +14628,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>219290</t>
+          <t>223984</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>280960</t>
+          <t>278454</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -14643,12 +14643,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>162480</t>
+          <t>159183</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>210310</t>
+          <t>211036</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -14678,12 +14678,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>400894</t>
+          <t>398439</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>476394</t>
+          <t>480744</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -14713,12 +14713,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
